--- a/fusionEntreesCDA/ig/StructureDefinition-fr-cda-hors-amm.xlsx
+++ b/fusionEntreesCDA/ig/StructureDefinition-fr-cda-hors-amm.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T09:38:40+00:00</t>
+    <t>2026-04-20T06:44:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionEntreesCDA/ig/StructureDefinition-fr-cda-hors-amm.xlsx
+++ b/fusionEntreesCDA/ig/StructureDefinition-fr-cda-hors-amm.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T06:44:24+00:00</t>
+    <t>2026-04-20T07:29:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -4584,7 +4584,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
         <v>167</v>
       </c>
@@ -4603,7 +4603,7 @@
         <v>75</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>74</v>
+        <v>160</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>74</v>
@@ -4988,7 +4988,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="37" hidden="true">
+    <row r="37">
       <c r="A37" t="s" s="2">
         <v>176</v>
       </c>
@@ -5003,13 +5003,13 @@
         <v>62</v>
       </c>
       <c r="F37" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>74</v>
+        <v>160</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>74</v>
@@ -5091,7 +5091,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
         <v>180</v>
       </c>
@@ -5106,13 +5106,13 @@
         <v>181</v>
       </c>
       <c r="F38" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>74</v>
+        <v>160</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>74</v>
@@ -5400,7 +5400,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="41" hidden="true">
+    <row r="41">
       <c r="A41" t="s" s="2">
         <v>194</v>
       </c>
@@ -5415,13 +5415,13 @@
         <v>195</v>
       </c>
       <c r="F41" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G41" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>74</v>
+        <v>160</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>74</v>

--- a/fusionEntreesCDA/ig/StructureDefinition-fr-cda-hors-amm.xlsx
+++ b/fusionEntreesCDA/ig/StructureDefinition-fr-cda-hors-amm.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T07:29:37+00:00</t>
+    <t>2026-04-20T13:53:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -5415,7 +5415,7 @@
         <v>195</v>
       </c>
       <c r="F41" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
         <v>75</v>
